--- a/out/MLP-S4_repeat_1_000007.xlsx
+++ b/out/MLP-S4_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.171991106271274</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003418900619039778</v>
+        <v>-0.0002394861812497256</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.941487474503797</v>
+        <v>2.760921971396211</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.171991106271274</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.889067777327875</v>
+        <v>5.526111829900075</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5910436062027098</v>
+        <v>0.4140125427739168</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.171991106271274</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.124377542311797</v>
+        <v>3.589509452425944</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7389968776464874</v>
+        <v>0.517650446177626</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.171991106271274</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.01142150787509</v>
+        <v>4.21086350471284</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.059348519486222</v>
+        <v>0.7420494596892927</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.391538717847709</v>
+        <v>5.177604110972209</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.133292732263334</v>
+        <v>0.7938459368700677</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.598855342662061</v>
+        <v>6.023301850896911</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.201061870469419</v>
+        <v>0.8413159482763287</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.571991106271275</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC45" t="n">
-        <v>9.867772888131244</v>
+        <v>6.912149357504775</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5420175497264333</v>
+        <v>0.379670905874038</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.571991106271275</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC46" t="n">
-        <v>9.749746562752724</v>
+        <v>6.829474614046627</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2617697027703341</v>
+        <v>0.1833630509307309</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.571991106271275</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC47" t="n">
-        <v>9.730843402744782</v>
+        <v>6.816233383465289</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1247254699899119</v>
+        <v>0.08736703470296096</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.571991106271275</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC48" t="n">
-        <v>9.718316758518943</v>
+        <v>6.807458725632082</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03695492354617681</v>
+        <v>0.02588624295656222</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.571991106271275</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC49" t="n">
-        <v>9.667369006372391</v>
+        <v>6.771770614288536</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02444478433527624</v>
+        <v>0.0171232648820775</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.571991106271275</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC50" t="n">
-        <v>9.679283629046649</v>
+        <v>6.780116658058981</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01250992513865628</v>
+        <v>0.008761056141228773</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC51" t="n">
-        <v>9.679841707677873</v>
+        <v>6.780506088177949</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006396364532109703</v>
+        <v>0.004479679822385395</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC52" t="n">
-        <v>9.680118074111546</v>
+        <v>6.780698192468043</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002401894036641896</v>
+        <v>0.00168058271056651</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC53" t="n">
-        <v>9.678519640511388</v>
+        <v>6.779577037790871</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001306759503841178</v>
+        <v>0.0009140566586660831</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC54" t="n">
-        <v>9.678729924668998</v>
+        <v>6.779722872100039</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006268103106938711</v>
+        <v>0.000437664582460989</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC55" t="n">
-        <v>9.678675956330659</v>
+        <v>6.779683563465503</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000385630181621711</v>
+        <v>0.0002685395226469412</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC56" t="n">
-        <v>9.678821095496229</v>
+        <v>6.779783755487863</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001998444623396049</v>
+        <v>0.0001380823128904778</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC57" t="n">
-        <v>9.678833942753206</v>
+        <v>6.779791267130939</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.391021994773259e-05</v>
+        <v>6.493651915496244e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC58" t="n">
-        <v>9.678822790189271</v>
+        <v>6.779781938266217</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.895731888813557e-05</v>
+        <v>3.97701232216949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.171991106271274</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC59" t="n">
-        <v>9.678845751531279</v>
+        <v>6.779796511205625</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.41402819409171e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC60" t="n">
-        <v>9.678835032551401</v>
+        <v>6.779787508627801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>7.35242988982542e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC61" t="n">
-        <v>9.678826607376267</v>
+        <v>6.779780042050807</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC62" t="n">
-        <v>9.678822682929461</v>
+        <v>6.779775786872636</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC63" t="n">
-        <v>9.678816671502869</v>
+        <v>6.779770064593606</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC64" t="n">
-        <v>9.678811578260735</v>
+        <v>6.779764995238237</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC65" t="n">
-        <v>9.678807213286767</v>
+        <v>6.779760630264268</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC66" t="n">
-        <v>9.678808304533222</v>
+        <v>6.779761721510726</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.171991106271274</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC67" t="n">
-        <v>9.678807614926086</v>
+        <v>6.779761031903589</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.171991106271274</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC68" t="n">
-        <v>9.678807645238489</v>
+        <v>6.779761062215991</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC69" t="n">
-        <v>9.678807455785979</v>
+        <v>6.779760872763481</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC70" t="n">
-        <v>9.678807508832682</v>
+        <v>6.779760925810185</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC71" t="n">
-        <v>9.678807561879383</v>
+        <v>6.779760978856887</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC72" t="n">
-        <v>9.678807523988882</v>
+        <v>6.779760940966384</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC73" t="n">
-        <v>9.678807395161176</v>
+        <v>6.779760812138678</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC74" t="n">
-        <v>9.678807251177268</v>
+        <v>6.77976066815477</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC75" t="n">
-        <v>9.678807092037159</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC76" t="n">
-        <v>9.678807145083864</v>
+        <v>6.779760562061365</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC77" t="n">
-        <v>9.678807092037159</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC78" t="n">
-        <v>9.678807092037159</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC79" t="n">
-        <v>9.67880691016275</v>
+        <v>6.779760327140253</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC80" t="n">
-        <v>9.678807076880959</v>
+        <v>6.779760493858461</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC81" t="n">
-        <v>9.67880727391157</v>
+        <v>6.779760690889072</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC82" t="n">
-        <v>9.678807114771461</v>
+        <v>6.779760531748964</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC83" t="n">
-        <v>9.678807152661962</v>
+        <v>6.779760569639465</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC84" t="n">
-        <v>9.678807349692574</v>
+        <v>6.779760766670075</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC85" t="n">
-        <v>9.678807326958273</v>
+        <v>6.779760743935774</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC86" t="n">
-        <v>9.678807175396264</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC87" t="n">
-        <v>9.678807099615261</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC88" t="n">
-        <v>9.678807198130565</v>
+        <v>6.779760615108068</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC89" t="n">
-        <v>9.678807205708665</v>
+        <v>6.779760622686168</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC90" t="n">
-        <v>9.678807470942179</v>
+        <v>6.779760887919682</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC91" t="n">
-        <v>9.678807175396264</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC92" t="n">
-        <v>9.678807417895477</v>
+        <v>6.779760834872978</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC93" t="n">
-        <v>9.678807501254582</v>
+        <v>6.779760918232084</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.171991106271274</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC94" t="n">
-        <v>9.678807334536371</v>
+        <v>6.779760751513875</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC95" t="n">
-        <v>9.678807523988882</v>
+        <v>6.779760940966384</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC96" t="n">
-        <v>9.678807175396264</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC97" t="n">
-        <v>9.678806970787553</v>
+        <v>6.779760387765055</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC98" t="n">
-        <v>9.678807084459059</v>
+        <v>6.779760501436561</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC99" t="n">
-        <v>9.678807099615261</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC100" t="n">
-        <v>9.678806864694149</v>
+        <v>6.779760281671651</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC101" t="n">
-        <v>9.67880692531895</v>
+        <v>6.779760342296453</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC102" t="n">
-        <v>9.678806796491244</v>
+        <v>6.779760213468746</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC103" t="n">
-        <v>9.678806932897052</v>
+        <v>6.779760349874554</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC104" t="n">
-        <v>9.678807107193361</v>
+        <v>6.779760524170863</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC105" t="n">
-        <v>9.678807251177268</v>
+        <v>6.77976066815477</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC106" t="n">
-        <v>9.678807084459059</v>
+        <v>6.779760501436561</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC107" t="n">
-        <v>9.678807076880959</v>
+        <v>6.779760493858461</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC108" t="n">
-        <v>9.678806788913144</v>
+        <v>6.779760205890646</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC109" t="n">
-        <v>9.678806804069344</v>
+        <v>6.779760221046847</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC110" t="n">
-        <v>9.678807031412358</v>
+        <v>6.779760448389859</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC111" t="n">
-        <v>9.678807016256155</v>
+        <v>6.779760433233658</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC112" t="n">
-        <v>9.678807122349562</v>
+        <v>6.779760539327063</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC113" t="n">
-        <v>9.678806849537946</v>
+        <v>6.779760266515449</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC114" t="n">
-        <v>9.678806948053252</v>
+        <v>6.779760365030755</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC115" t="n">
-        <v>9.678807099615261</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC116" t="n">
-        <v>9.678807114771461</v>
+        <v>6.779760531748964</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC117" t="n">
-        <v>9.678807092037159</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC118" t="n">
-        <v>9.678807175396264</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC119" t="n">
-        <v>9.67880727391157</v>
+        <v>6.779760690889072</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC120" t="n">
-        <v>9.678807107193361</v>
+        <v>6.779760524170863</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC121" t="n">
-        <v>9.678807092037159</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC122" t="n">
-        <v>9.678807061724758</v>
+        <v>6.779760478702261</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9824533321832731</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC123" t="n">
-        <v>9.678807046568558</v>
+        <v>6.77976046354606</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC124" t="n">
-        <v>9.678807084459059</v>
+        <v>6.779760501436561</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC125" t="n">
-        <v>9.678807099615261</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC126" t="n">
-        <v>9.678807092037159</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_1_000007.xlsx
+++ b/out/MLP-S4_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.171991106271274</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.171991106271274</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003418900619039778</v>
+        <v>-0.0002623813901516842</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.941487474503797</v>
+        <v>3.024869915980737</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.889067777327875</v>
+        <v>6.054415734957099</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5910436062027098</v>
+        <v>0.4535927371672775</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.124377542311797</v>
+        <v>3.932671501812836</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7389968776464874</v>
+        <v>0.5671385109910624</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.01142150787509</v>
+        <v>4.613427820317648</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.059348519486222</v>
+        <v>0.8129903659070732</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.391538717847709</v>
+        <v>5.672590102504499</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.133292732263334</v>
+        <v>0.8697383065037521</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC44" t="n">
-        <v>8.598855342662061</v>
+        <v>6.599137661357742</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.201061870469419</v>
+        <v>0.9217480387657582</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.571991106271275</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC45" t="n">
-        <v>9.867772888131244</v>
+        <v>7.572960549407076</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5420175497264333</v>
+        <v>0.4159670806482268</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.571991106271275</v>
+        <v>1.929365330014588</v>
       </c>
       <c r="JC46" t="n">
-        <v>9.749746562752724</v>
+        <v>7.482382035715176</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2617697027703341</v>
+        <v>0.2008930875365338</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.571991106271275</v>
+        <v>1.929365330014588</v>
       </c>
       <c r="JC47" t="n">
-        <v>9.730843402744782</v>
+        <v>7.467874909640975</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1247254699899119</v>
+        <v>0.09571957524321374</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.571991106271275</v>
+        <v>1.929365330014588</v>
       </c>
       <c r="JC48" t="n">
-        <v>9.718316758518943</v>
+        <v>7.45826137500307</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03695492354617681</v>
+        <v>0.0283610424557627</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.571991106271275</v>
+        <v>1.929365330014588</v>
       </c>
       <c r="JC49" t="n">
-        <v>9.667369006372391</v>
+        <v>7.41916142508387</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02444478433527624</v>
+        <v>0.01875977198652657</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.571991106271275</v>
+        <v>1.116920886939263</v>
       </c>
       <c r="JC50" t="n">
-        <v>9.679283629046649</v>
+        <v>7.428305353056591</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01250992513865628</v>
+        <v>0.009599385901283428</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.3044764438639379</v>
       </c>
       <c r="JC51" t="n">
-        <v>9.679841707677873</v>
+        <v>7.428732501785025</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006396364532109703</v>
+        <v>0.004908517892943461</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC52" t="n">
-        <v>9.680118074111546</v>
+        <v>7.428943453758076</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002401894036641896</v>
+        <v>0.001841799197926486</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC53" t="n">
-        <v>9.678519640511388</v>
+        <v>7.427715569094479</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001306759503841178</v>
+        <v>0.001001507292255495</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC54" t="n">
-        <v>9.678729924668998</v>
+        <v>7.427875823883723</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006268103106938711</v>
+        <v>0.0004797852698405803</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC55" t="n">
-        <v>9.678675956330659</v>
+        <v>7.427833220380899</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000385630181621711</v>
+        <v>0.0002951063108176873</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC56" t="n">
-        <v>9.678821095496229</v>
+        <v>7.427943610494575</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001998444623396049</v>
+        <v>0.0001524934810952741</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC57" t="n">
-        <v>9.678833942753206</v>
+        <v>7.427952332254967</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.391021994773259e-05</v>
+        <v>7.093107793967352e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC58" t="n">
-        <v>9.678822790189271</v>
+        <v>7.427942602032297</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.895731888813557e-05</v>
+        <v>4.360756235498304e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC59" t="n">
-        <v>9.678845751531279</v>
+        <v>7.427959133041939</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.41402819409171e-05</v>
+        <v>1.7146614275097e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC60" t="n">
-        <v>9.678835032551401</v>
+        <v>7.427949672945725</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>7.35242988982542e-06</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC61" t="n">
-        <v>9.678826607376267</v>
+        <v>7.427941932304619</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC62" t="n">
-        <v>9.678822682929461</v>
+        <v>7.427937759133026</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC63" t="n">
-        <v>9.678816671502869</v>
+        <v>7.427932036853996</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.304476443863938</v>
       </c>
       <c r="JC64" t="n">
-        <v>9.678811578260735</v>
+        <v>7.427926967498626</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC65" t="n">
-        <v>9.678807213286767</v>
+        <v>7.427922602524658</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC66" t="n">
-        <v>9.678808304533222</v>
+        <v>7.427923693771114</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.171991106271274</v>
+        <v>2.129365330014588</v>
       </c>
       <c r="JC67" t="n">
-        <v>9.678807614926086</v>
+        <v>7.427923004163978</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.171991106271274</v>
+        <v>1.316920886939263</v>
       </c>
       <c r="JC68" t="n">
-        <v>9.678807645238489</v>
+        <v>7.427923034476381</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC69" t="n">
-        <v>9.678807455785979</v>
+        <v>7.42792284502387</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC70" t="n">
-        <v>9.678807508832682</v>
+        <v>7.427922898070574</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC71" t="n">
-        <v>9.678807561879383</v>
+        <v>7.427922951117275</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC72" t="n">
-        <v>9.678807523988882</v>
+        <v>7.427922913226774</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC73" t="n">
-        <v>9.678807395161176</v>
+        <v>7.427922784399068</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC74" t="n">
-        <v>9.678807251177268</v>
+        <v>7.42792264041516</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC75" t="n">
-        <v>9.678807092037159</v>
+        <v>7.427922481275052</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC76" t="n">
-        <v>9.678807145083864</v>
+        <v>7.427922534321755</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC77" t="n">
-        <v>9.678807092037159</v>
+        <v>7.427922481275052</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC78" t="n">
-        <v>9.678807092037159</v>
+        <v>7.427922481275052</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC79" t="n">
-        <v>9.67880691016275</v>
+        <v>7.427922299400643</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC80" t="n">
-        <v>9.678807076880959</v>
+        <v>7.427922466118852</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC81" t="n">
-        <v>9.67880727391157</v>
+        <v>7.427922663149461</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC82" t="n">
-        <v>9.678807114771461</v>
+        <v>7.427922504009353</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC83" t="n">
-        <v>9.678807152661962</v>
+        <v>7.427922541899854</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC84" t="n">
-        <v>9.678807349692574</v>
+        <v>7.427922738930466</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC85" t="n">
-        <v>9.678807326958273</v>
+        <v>7.427922716196164</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC86" t="n">
-        <v>9.678807175396264</v>
+        <v>7.427922564634155</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC87" t="n">
-        <v>9.678807099615261</v>
+        <v>7.427922488853153</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC88" t="n">
-        <v>9.678807198130565</v>
+        <v>7.427922587368457</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC89" t="n">
-        <v>9.678807205708665</v>
+        <v>7.427922594946557</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC90" t="n">
-        <v>9.678807470942179</v>
+        <v>7.427922860180071</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC91" t="n">
-        <v>9.678807175396264</v>
+        <v>7.427922564634155</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC92" t="n">
-        <v>9.678807417895477</v>
+        <v>7.427922807133369</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC93" t="n">
-        <v>9.678807501254582</v>
+        <v>7.427922890492473</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.171991106271274</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC94" t="n">
-        <v>9.678807334536371</v>
+        <v>7.427922723774263</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3824533321832731</v>
+        <v>0.504476443863938</v>
       </c>
       <c r="JC95" t="n">
-        <v>9.678807523988882</v>
+        <v>7.427922913226774</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC96" t="n">
-        <v>9.678807175396264</v>
+        <v>7.427922564634155</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.3079679992113873</v>
       </c>
       <c r="JC97" t="n">
-        <v>9.678806970787553</v>
+        <v>7.427922360025445</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC98" t="n">
-        <v>9.678807084459059</v>
+        <v>7.427922473696951</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC99" t="n">
-        <v>9.678807099615261</v>
+        <v>7.427922488853153</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC100" t="n">
-        <v>9.678806864694149</v>
+        <v>7.42792225393204</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC101" t="n">
-        <v>9.67880692531895</v>
+        <v>7.427922314556842</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC102" t="n">
-        <v>9.678806796491244</v>
+        <v>7.427922185729137</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC103" t="n">
-        <v>9.678806932897052</v>
+        <v>7.427922322134943</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC104" t="n">
-        <v>9.678807107193361</v>
+        <v>7.427922496431252</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC105" t="n">
-        <v>9.678807251177268</v>
+        <v>7.42792264041516</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC106" t="n">
-        <v>9.678807084459059</v>
+        <v>7.427922473696951</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC107" t="n">
-        <v>9.678807076880959</v>
+        <v>7.427922466118852</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC108" t="n">
-        <v>9.678806788913144</v>
+        <v>7.427922178151036</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC109" t="n">
-        <v>9.678806804069344</v>
+        <v>7.427922193307236</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC110" t="n">
-        <v>9.678807031412358</v>
+        <v>7.427922420650249</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC111" t="n">
-        <v>9.678807016256155</v>
+        <v>7.427922405494047</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC112" t="n">
-        <v>9.678807122349562</v>
+        <v>7.427922511587454</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC113" t="n">
-        <v>9.678806849537946</v>
+        <v>7.427922238775838</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC114" t="n">
-        <v>9.678806948053252</v>
+        <v>7.427922337291144</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC115" t="n">
-        <v>9.678807099615261</v>
+        <v>7.427922488853153</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC116" t="n">
-        <v>9.678807114771461</v>
+        <v>7.427922504009353</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC117" t="n">
-        <v>9.678807092037159</v>
+        <v>7.427922481275052</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC118" t="n">
-        <v>9.678807175396264</v>
+        <v>7.427922564634155</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC119" t="n">
-        <v>9.67880727391157</v>
+        <v>7.427922663149461</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC120" t="n">
-        <v>9.678807107193361</v>
+        <v>7.427922496431252</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC121" t="n">
-        <v>9.678807092037159</v>
+        <v>7.427922481275052</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC122" t="n">
-        <v>9.678807061724758</v>
+        <v>7.42792245096265</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC123" t="n">
-        <v>9.678807046568558</v>
+        <v>7.427922435806449</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC124" t="n">
-        <v>9.678807084459059</v>
+        <v>7.427922473696951</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC125" t="n">
-        <v>9.678807099615261</v>
+        <v>7.427922488853153</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9824533321832731</v>
+        <v>-0.5079679992113874</v>
       </c>
       <c r="JC126" t="n">
-        <v>9.678807092037159</v>
+        <v>7.427922481275052</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_1_000007.xlsx
+++ b/out/MLP-S4_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.389819324016571</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4010814130306244</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3883104622364044</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.304476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5581567883491516</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.504476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4726549983024597</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.504476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4193157255649567</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3079679992113873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3898263573646545</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4108645021915436</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4066819846630096</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4089604914188385</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4027018547058105</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3930954337120056</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4206462800502777</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4106921553611755</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4414951801300049</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4158404469490051</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4211357533931732</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.403473436832428</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4414010345935822</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.444735586643219</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4838602542877197</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.504476443863938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5648192167282104</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.504476443863938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4914712905883789</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.504476443863938</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.456476092338562</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3079679992113873</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4428083896636963</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3079679992113873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4357521831989288</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.425571471452713</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.482306033372879</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4674074351787567</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4520951807498932</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4378016889095306</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4325675666332245</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4418570399284363</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4508416056632996</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.504476443863938</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5556173324584961</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.316920886939263</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7345424294471741</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6237232089042664</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.129365330014588</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5919308066368103</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.129365330014588</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002623813901516842</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.024869915980737</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5848137140274048</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.054415734957099</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4535927371672775</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5718072652816772</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.932671501812836</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5671385109910624</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5269412994384766</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.613427820317648</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8129903659070732</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6264886856079102</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.672590102504499</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8697383065037521</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6898642182350159</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.129365330014588</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.599137661357742</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9217480387657582</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7463858127593994</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.129365330014588</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.572960549407076</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4159670806482268</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.7933135032653809</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.929365330014588</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.482382035715176</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2008930875365338</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5368085503578186</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.929365330014588</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.467874909640975</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09571957524321374</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.658003032207489</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.929365330014588</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.45826137500307</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0283610424557627</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5032681226730347</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.929365330014588</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.41916142508387</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01875977198652657</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.51258784532547</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.116920886939263</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.428305353056591</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.009599385901283428</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.418554812669754</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3044764438639379</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.428732501785025</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004908517892943461</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4642638862133026</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.428943453758076</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001841799197926486</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4562734365463257</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.427715569094479</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001001507292255495</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.411493182182312</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.427875823883723</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004797852698405803</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4172805845737457</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.427833220380899</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002951063108176873</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4502419829368591</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.427943610494575</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001524934810952741</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3502066731452942</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.304476443863938</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.427952332254967</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.093107793967352e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7355363965034485</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.316920886939263</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.427942602032297</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.360756235498304e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5770518183708191</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.316920886939263</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.427959133041939</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.7146614275097e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4039334058761597</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.504476443863938</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.427949672945725</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3771922588348389</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3079679992113873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.427941932304619</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.406801849603653</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.427937759133026</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.42489093542099</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.427932036853996</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4724523723125458</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.304476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.427926967498626</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7118952870368958</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.316920886939263</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.427922602524658</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9176469445228577</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.129365330014588</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.427923693771114</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7410688400268555</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.129365330014588</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.427923004163978</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.5505326986312866</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.316920886939263</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.427923034476381</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4838416278362274</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.504476443863938</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.42792284502387</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4885279834270477</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.427922898070574</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3811448514461517</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.427922951117275</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3179013431072235</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.427922913226774</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3815269768238068</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.427922784399068</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.381890207529068</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.42792264041516</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3485641181468964</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.427922481275052</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3730289936065674</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.427922534321755</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3470693528652191</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.427922481275052</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3674753904342651</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.427922481275052</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3933448791503906</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.427922299400643</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4010837972164154</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.427922466118852</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3579113483428955</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.427922663149461</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3042378425598145</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.427922504009353</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3767355382442474</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.427922541899854</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4787798523902893</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.427922738930466</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3897688388824463</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.427922716196164</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3360657393932343</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.427922564634155</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.336378276348114</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.427922488853153</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3687131404876709</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.427922587368457</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.470300555229187</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.427922594946557</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4458452165126801</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.427922860180071</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4071437120437622</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.427922564634155</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4960930347442627</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.427922807133369</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4326227009296417</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.504476443863938</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.427922890492473</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6150945425033569</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.504476443863938</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.427922723774263</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4861428141593933</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.504476443863938</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.427922913226774</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4183992147445679</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3079679992113873</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.427922564634155</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3575413525104523</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3079679992113873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.427922360025445</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3386649191379547</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.427922473696951</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3950106203556061</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.427922488853153</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3764428794384003</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.42792225393204</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3367372453212738</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.427922314556842</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3399359285831451</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.427922185729137</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4830016791820526</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.427922322134943</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3865290880203247</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.427922496431252</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3371174037456512</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.42792264041516</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3474848866462708</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.427922473696951</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3395743370056152</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.427922466118852</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2829253673553467</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.427922178151036</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3098011314868927</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.427922193307236</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3399912118911743</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.427922420650249</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4044097065925598</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.427922405494047</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3421477973461151</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.427922511587454</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3468241393566132</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.427922238775838</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3643191158771515</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.427922337291144</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3766398429870605</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.427922488853153</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3733923137187958</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.427922504009353</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3994898200035095</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.427922481275052</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4184557199478149</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.427922564634155</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3468339145183563</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.427922663149461</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3366145491600037</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.427922496431252</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3507561981678009</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.427922481275052</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.369776576757431</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.42792245096265</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3715722560882568</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.427922435806449</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3403083384037018</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5079679992113874</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.427922473696951</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3615793287754059</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.4400000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.427922488853153</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3993572592735291</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5079679992113874</v>
+        <v>0.7200000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.427922481275052</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_1_000007.xlsx
+++ b/out/MLP-S4_repeat_1_000007.xlsx
@@ -73289,7 +73289,7 @@
         <v>0.4071437120437622</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>4.989783696705144</v>
@@ -74084,7 +74084,7 @@
         <v>0.4960930347442627</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.989783939204357</v>
@@ -74879,7 +74879,7 @@
         <v>0.4326227009296417</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>4.989784022563462</v>
@@ -75674,7 +75674,7 @@
         <v>0.6150945425033569</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>4.989783855845253</v>
@@ -76469,7 +76469,7 @@
         <v>0.4861428141593933</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>4.989784045297762</v>
